--- a/project-management/skills/pmo-pert-estimate/examples/scenario-3-mobile-app/pert-estimate.xlsx
+++ b/project-management/skills/pmo-pert-estimate/examples/scenario-3-mobile-app/pert-estimate.xlsx
@@ -3982,59 +3982,59 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>Key mobile developer unavailability</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t>Organizational</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="21">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="H4">
+      <c r="H4" s="21">
         <f>IF(G4&gt;=15,"CRITICAL",IF(G4&gt;=10,"HIGH",IF(G4&gt;=5,"MEDIUM","LOW")))</f>
         <v/>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="21" t="inlineStr">
         <is>
           <t>Mitigate</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t>Cross-train backend developer on mobile framework</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="21" t="inlineStr">
         <is>
           <t>PO</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="21">
         <f>L4*550</f>
         <v/>
       </c>
